--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,42 +413,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-26</t>
+          <t>Ventas 2025-08-01 / 2025-08-02</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Venue Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gross Sales</t>
-        </is>
-      </c>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Net Sales</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Discounts</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Voids</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Bill Count</t>
@@ -458,155 +446,145 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#001 Florida Mall Orlando FL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>83655.07000000001</v>
-      </c>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>83655.07000000001</v>
-      </c>
-      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#002 American Dream Mall NJ</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>72297.95</v>
-      </c>
+          <t>Barcelona 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>72297.95</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>16092.24</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4506</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#003 Sawgrass Mills Mall FL</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>97878.12</v>
-      </c>
+          <t>Barcelona 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>97878.12</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>6771.27</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>6453</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#004 Weston Town Center FL</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>59578.76</v>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>59578.76</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
+        <v>3599.59</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>3669</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#005 Vineland Orlando FL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>19447.81</v>
-      </c>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>19447.81</v>
-      </c>
-      <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#006 Aventura, FL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28028.28</v>
-      </c>
+          <t>Málaga 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>28028.28</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
+        <v>8959.139999999999</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1604</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REPORT SUMMARY (6 entries)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>360885.99</v>
-      </c>
+          <t>Málaga 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>360885.99</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+        <v>3755.82</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>10111.55</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>10279.89</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>1193</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-02</t>
+          <t>Ventas 2025-08-01 / 2025-08-09</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>16092.24</v>
+        <v>67802.3</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1658</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6771.27</v>
+        <v>29664.35</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>823</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>3599.59</v>
+        <v>13590</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>445</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8959.139999999999</v>
+        <v>39336.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1083</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3755.82</v>
+        <v>16467.43</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>445</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>10111.55</v>
+        <v>42247.88</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1081</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>10279.89</v>
+        <v>45426.53</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1193</v>
+        <v>5133</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-09</t>
+          <t>Ventas 2025-08-01 / 2025-08-16</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>67802.3</v>
+        <v>120128.72</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>7176</v>
+        <v>12687</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>29664.35</v>
+        <v>51776.77</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3460</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>13590</v>
+        <v>26379.05</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1678</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>39336.55</v>
+        <v>72607.52</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>4814</v>
+        <v>8750</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>16467.43</v>
+        <v>28430.89</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1998</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>42247.88</v>
+        <v>75653.5</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>4441</v>
+        <v>7838</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>45426.53</v>
+        <v>78513.27</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>5133</v>
+        <v>8877</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-16</t>
+          <t>Ventas 2025-08-01 / 2025-08-23</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>120128.72</v>
+        <v>166823.31</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>12687</v>
+        <v>17812</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>51776.77</v>
+        <v>70545.28999999999</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>6100</v>
+        <v>8360</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>26379.05</v>
+        <v>37506.4</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>3187</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>72607.52</v>
+        <v>105033.48</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>8750</v>
+        <v>12602</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>28430.89</v>
+        <v>40427.01</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>3489</v>
+        <v>4961</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>75653.5</v>
+        <v>108484.65</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>7838</v>
+        <v>11240</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>78513.27</v>
+        <v>112285.63</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>8877</v>
+        <v>12671</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-23</t>
+          <t>Ventas 2025-08-01 / 2025-08-30</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>166823.31</v>
+        <v>213167.94</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>17812</v>
+        <v>22974</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>70545.28999999999</v>
+        <v>88323.84</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>8360</v>
+        <v>10699</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>37506.4</v>
+        <v>47346.1</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4531</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>105033.48</v>
+        <v>132958.79</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>12602</v>
+        <v>16090</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>40427.01</v>
+        <v>51139.01</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>4961</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>108484.65</v>
+        <v>138960.39</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>11240</v>
+        <v>14486</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>112285.63</v>
+        <v>144684.14</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>12671</v>
+        <v>16495</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-30</t>
+          <t>Ventas 2025-09-01 / 2025-09-06</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>213167.94</v>
+        <v>35215.96</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>22974</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>88323.84</v>
+        <v>14084.01</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>10699</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>47346.1</v>
+        <v>6847.08</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>5758</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>132958.79</v>
+        <v>20194.83</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>16090</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>51139.01</v>
+        <v>7141.78</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>6311</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>138960.39</v>
+        <v>23551.29</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>14486</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>144684.14</v>
+        <v>25287.09</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>16495</v>
+        <v>3091</v>
       </c>
     </row>
   </sheetData>
